--- a/data/trans_bre/P32B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,67</t>
+          <t>-1,45; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,01</t>
+          <t>-6,14; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,56</t>
+          <t>-3,41; 2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 13,22</t>
+          <t>0,07; 12,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 867,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 37,5</t>
+          <t>-85,86; 36,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 289,88</t>
+          <t>-100,0; 218,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,3</t>
+          <t>-0,7; 2,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,58</t>
+          <t>-4,64; -0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,26</t>
+          <t>-3,75; 1,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -0,79</t>
+          <t>-9,51; -0,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,02</t>
+          <t>-100,0; 59,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,04; 72,79</t>
+          <t>-80,43; 84,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,78</t>
+          <t>-100,0; 699,44</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,57</t>
+          <t>-0,72; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,96</t>
+          <t>-4,7; -1,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,49</t>
+          <t>-2,72; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,46</t>
+          <t>-1,41; 2,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,3</t>
+          <t>-100,0; -20,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,38</t>
+          <t>-100,0; 115,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,53</t>
+          <t>-3,22; -0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,27</t>
+          <t>-3,85; 0,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,85</t>
+          <t>-1,63; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,42</t>
+          <t>-100,0; 127,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,47; 528,49</t>
+          <t>-87,09; 546,68</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,17</t>
+          <t>-5,56; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,36</t>
+          <t>-5,2; -0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -0,39</t>
+          <t>-4,28; -0,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,5</t>
+          <t>-3,84; 2,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 316,94</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,24; 157,26</t>
+          <t>-75,76; 133,09</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -0,64</t>
+          <t>-7,97; -0,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,03</t>
+          <t>-3,23; -0,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,0</t>
+          <t>-6,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 0,0</t>
+          <t>-12,66; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,22; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 4,86</t>
+          <t>-2,91; 5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,13</t>
+          <t>-0,46; 1,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -1,28</t>
+          <t>-3,14; -1,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,0; -0,17</t>
+          <t>-1,94; -0,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,53</t>
+          <t>-1,9; 0,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 229,68</t>
+          <t>-46,95; 198,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -51,14</t>
+          <t>-90,03; -46,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -6,63</t>
+          <t>-75,0; -5,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 38,15</t>
+          <t>-74,6; 26,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3993,48%</t>
+          <t>450,56%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,81</t>
+          <t>-1,31; 3,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,86</t>
+          <t>-5,73; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,14</t>
+          <t>-3,27; 2,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 12,74</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 867,17</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 36,7</t>
+          <t>-82,1; 38,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 218,74</t>
+          <t>-86,76; 320,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-3,81</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-86,76%</t>
+          <t>-87,14%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,45</t>
+          <t>-0,57; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,57</t>
+          <t>-4,52; -0,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,41</t>
+          <t>-3,85; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -0,5</t>
+          <t>-9,04; -1,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,41</t>
+          <t>-100,0; 29,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 84,2</t>
+          <t>-84,2; 90,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 699,44</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>-16,14%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,39</t>
+          <t>-0,91; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -1,1</t>
+          <t>-4,43; -0,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,35</t>
+          <t>-2,8; 0,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,41</t>
+          <t>-2,18; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,74</t>
+          <t>-100,0; 72,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,94</t>
+          <t>-100,0; 205,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,54</t>
+          <t>-3,26; -0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,51</t>
+          <t>-3,59; 0,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,72</t>
+          <t>-1,56; 2,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,2</t>
+          <t>-100,0; 171,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 546,68</t>
+          <t>-79,25; 383,07</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,35%</t>
+          <t>-20,33%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,76</t>
+          <t>-5,88; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -0,35</t>
+          <t>-5,77; -0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,39</t>
+          <t>-4,54; -0,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,14</t>
+          <t>-3,46; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,76; 133,09</t>
+          <t>-76,64; 133,89</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-87,9%</t>
+          <t>-63,79%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,64</t>
+          <t>-7,89; -0,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-2,7; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,1</t>
+          <t>-2,85; 0,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-16,31%</t>
+          <t>-17,96%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,0</t>
+          <t>-6,89; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 0,0</t>
+          <t>-12,78; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,3</t>
+          <t>-2,86; 4,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-32,79%</t>
+          <t>-12,52%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,11</t>
+          <t>-0,49; 1,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -1,22</t>
+          <t>-3,12; -1,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,18</t>
+          <t>-1,99; -0,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,44</t>
+          <t>-1,39; 1,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 198,62</t>
+          <t>-48,24; 199,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,03; -46,31</t>
+          <t>-89,95; -46,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-75,0; -5,95</t>
+          <t>-75,36; -1,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 26,98</t>
+          <t>-54,2; 69,77</t>
         </is>
       </c>
     </row>
